--- a/Excel/Talk.xlsx
+++ b/Excel/Talk.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Unity\MightyFinalFight\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D567E006-19A8-4EAE-B7A0-DC5398D3D42F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC41FAF6-78C8-47A8-A710-E1411C7B617C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5070" yWindow="5070" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -556,7 +556,9 @@
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
+      <c r="E4" s="1">
+        <v>3333</v>
+      </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="1"/>

--- a/Excel/Talk.xlsx
+++ b/Excel/Talk.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Unity\MightyFinalFight\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MightyFinalFight\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC41FAF6-78C8-47A8-A710-E1411C7B617C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{744DA871-656B-4E26-AF93-8ADE1E123C28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5070" yWindow="5070" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="32">
   <si>
     <t>SheetName</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -55,56 +55,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>HEN-HEN. I AM THRASHER.</t>
-  </si>
-  <si>
-    <t>RULER OF THIS CITY.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BOW DOWN BEFORE ME! </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> I AM SUPERIOR.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MAYBE YOU'RE STRONGER THAN YOU LOOK.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>WHY DON'T YOU JOIN US?</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>HEN-HEH. I DON'T BELIEVE YOU.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>YOU'RE TOO MUCH OF A MAMA'S BOY.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>YOU DARE REFUSE THE MAD GREA GANG?</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>THOSE WHO OFFEND ME MUST DIE!</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> WAAAAA!</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> ARGHHHHH!</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DON'T YOU KNOW I RULE THE STREETS!?</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>string</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -141,11 +91,55 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>[{"content":"YES","talkId":1004},{"content":"NO","talkId":1012,"effect":{"effectId":1,"effectValue":20}}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{"content":"YES","talkId":1007},{"content":"NO","talkId":1009}]</t>
+    <t>Talk1001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Talk1002</t>
+  </si>
+  <si>
+    <t>Talk1003</t>
+  </si>
+  <si>
+    <t>Talk1004</t>
+  </si>
+  <si>
+    <t>Talk1005</t>
+  </si>
+  <si>
+    <t>Talk1006</t>
+  </si>
+  <si>
+    <t>Talk1007</t>
+  </si>
+  <si>
+    <t>Talk1008</t>
+  </si>
+  <si>
+    <t>Talk1009</t>
+  </si>
+  <si>
+    <t>Talk1010</t>
+  </si>
+  <si>
+    <t>Talk1011</t>
+  </si>
+  <si>
+    <t>Talk1012</t>
+  </si>
+  <si>
+    <t>Talk1013</t>
+  </si>
+  <si>
+    <t>[{"content":"Talk1003_Select1","talkId":1004},{"content":"Talk1003_Select2","talkId":1012,"effect":{"effectId":1,"effectValue":20}}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"content":"Talk1006_Select1","talkId":1007},{"content":"Talk1006_Select2","talkId":1009}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"content":"Talk1011_Select1","talkId":1004},{"content":"Talk1011_Select2","talkId":1012,"effect":{"effectId":1,"effectValue":20}}]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -153,7 +147,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -173,6 +167,11 @@
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9.8000000000000007"/>
+      <name val="JetBrains Mono"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -195,13 +194,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -484,16 +486,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F17"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="24.5" customWidth="1"/>
     <col min="2" max="3" width="21.375" customWidth="1"/>
     <col min="4" max="4" width="51" customWidth="1"/>
-    <col min="5" max="5" width="88.5" customWidth="1"/>
+    <col min="5" max="5" width="103.875" customWidth="1"/>
     <col min="6" max="6" width="32.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -501,19 +503,19 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -521,46 +523,44 @@
         <v>2</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="1"/>
       <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
-      <c r="E4" s="1">
-        <v>3333</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="E4" s="1"/>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>1001</v>
@@ -568,15 +568,15 @@
       <c r="C5" s="1">
         <v>2005</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>7</v>
+      <c r="D5" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="E5" s="1"/>
-      <c r="F5">
+      <c r="F5" s="1">
         <v>1002</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6">
       <c r="A6" s="1"/>
       <c r="B6" s="1">
         <v>1002</v>
@@ -584,15 +584,15 @@
       <c r="C6" s="1">
         <v>2005</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>8</v>
+      <c r="D6" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="E6" s="1"/>
-      <c r="F6">
+      <c r="F6" s="1">
         <v>1003</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6">
       <c r="A7" s="1"/>
       <c r="B7" s="1">
         <v>1003</v>
@@ -600,14 +600,15 @@
       <c r="C7" s="1">
         <v>2005</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>9</v>
+      <c r="D7" s="3" t="s">
+        <v>18</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F7" s="1"/>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" s="2"/>
       <c r="B8" s="1">
         <v>1004</v>
@@ -615,15 +616,15 @@
       <c r="C8" s="1">
         <v>2005</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>10</v>
+      <c r="D8" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="E8" s="2"/>
-      <c r="F8">
+      <c r="F8" s="1">
         <v>1005</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6">
       <c r="A9" s="2"/>
       <c r="B9" s="1">
         <v>1005</v>
@@ -631,14 +632,14 @@
       <c r="C9" s="1">
         <v>2005</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9">
+      <c r="D9" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F9" s="1">
         <v>1006</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6">
       <c r="A10" s="2"/>
       <c r="B10" s="1">
         <v>1006</v>
@@ -646,14 +647,15 @@
       <c r="C10" s="1">
         <v>2005</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>12</v>
+      <c r="D10" s="3" t="s">
+        <v>21</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F10" s="1"/>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11" s="2"/>
       <c r="B11" s="1">
         <v>1007</v>
@@ -661,15 +663,15 @@
       <c r="C11" s="1">
         <v>2005</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>13</v>
+      <c r="D11" s="3" t="s">
+        <v>22</v>
       </c>
       <c r="E11" s="2"/>
-      <c r="F11">
+      <c r="F11" s="1">
         <v>1008</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6">
       <c r="A12" s="2"/>
       <c r="B12" s="2">
         <v>1008</v>
@@ -677,12 +679,13 @@
       <c r="C12" s="1">
         <v>2005</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>14</v>
+      <c r="D12" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="E12" s="2"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F12" s="1"/>
+    </row>
+    <row r="13" spans="1:6">
       <c r="A13" s="2"/>
       <c r="B13" s="2">
         <v>1009</v>
@@ -690,59 +693,60 @@
       <c r="C13" s="1">
         <v>2005</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>15</v>
+      <c r="D13" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="E13" s="2"/>
-      <c r="F13">
-        <v>1013</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F13" s="1">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
       <c r="B14" s="2">
         <v>1010</v>
       </c>
       <c r="C14" s="1">
         <v>2005</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>17</v>
+      <c r="D14" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="E14" s="2"/>
-      <c r="F14">
-        <v>1012</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F14" s="1">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
       <c r="B15" s="2">
         <v>1011</v>
       </c>
       <c r="C15" s="1">
         <v>2005</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>19</v>
+      <c r="D15" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+      <c r="F15" s="1"/>
+    </row>
+    <row r="16" spans="1:6">
       <c r="B16" s="2">
         <v>1012</v>
       </c>
       <c r="C16" s="1">
         <v>2005</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>18</v>
+      <c r="D16" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="E16" s="2"/>
-      <c r="F16">
+      <c r="F16" s="1">
         <v>1013</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5">
       <c r="A17" s="2"/>
       <c r="B17" s="2">
         <v>1013</v>
@@ -750,13 +754,14 @@
       <c r="C17" s="1">
         <v>2005</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>16</v>
+      <c r="D17" s="3" t="s">
+        <v>28</v>
       </c>
       <c r="E17" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Excel/Talk.xlsx
+++ b/Excel/Talk.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MightyFinalFight\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Work\Unity\MightyFinalFight\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{744DA871-656B-4E26-AF93-8ADE1E123C28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6B99487-C1DC-452B-95A2-8EEA0F2801C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Talk" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
